--- a/output/все-товары.xlsx
+++ b/output/все-товары.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ78"/>
+  <dimension ref="A1:CJ81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13163,6 +13163,490 @@
       </c>
       <c r="CJ78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Вставка в ручку APRILE GUAVA TH WC под окраску</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Aprile</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>00-00005543</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>00-00005543</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>300</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-th-wc-1000x1000.png</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Италия</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Цинк</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr"/>
+      <c r="AP79" t="inlineStr"/>
+      <c r="AQ79" t="inlineStr"/>
+      <c r="AR79" t="inlineStr"/>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AU79" t="inlineStr"/>
+      <c r="AV79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr"/>
+      <c r="AX79" t="inlineStr"/>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr"/>
+      <c r="BA79" t="inlineStr"/>
+      <c r="BB79" t="inlineStr"/>
+      <c r="BC79" t="inlineStr"/>
+      <c r="BD79" t="inlineStr"/>
+      <c r="BE79" t="inlineStr"/>
+      <c r="BF79" t="inlineStr"/>
+      <c r="BG79" t="inlineStr"/>
+      <c r="BH79" t="inlineStr"/>
+      <c r="BI79" t="inlineStr"/>
+      <c r="BJ79" t="inlineStr"/>
+      <c r="BK79" t="inlineStr"/>
+      <c r="BL79" t="inlineStr"/>
+      <c r="BM79" t="inlineStr"/>
+      <c r="BN79" t="inlineStr"/>
+      <c r="BO79" t="inlineStr"/>
+      <c r="BP79" t="inlineStr"/>
+      <c r="BQ79" t="inlineStr"/>
+      <c r="BR79" t="inlineStr"/>
+      <c r="BS79" t="inlineStr"/>
+      <c r="BT79" t="inlineStr"/>
+      <c r="BU79" t="inlineStr"/>
+      <c r="BV79" t="inlineStr"/>
+      <c r="BW79" t="inlineStr"/>
+      <c r="BX79" t="inlineStr"/>
+      <c r="BY79" t="inlineStr"/>
+      <c r="BZ79" t="inlineStr"/>
+      <c r="CA79" t="inlineStr"/>
+      <c r="CB79" t="inlineStr"/>
+      <c r="CC79" t="inlineStr"/>
+      <c r="CD79" t="inlineStr"/>
+      <c r="CE79" t="inlineStr">
+        <is>
+          <t>https://furnitura96.ru/vstavka-v-ruchku-aprile-guava-th-wc-pod-okrasku/</t>
+        </is>
+      </c>
+      <c r="CF79" t="inlineStr">
+        <is>
+          <t>Фурнитура для межкомнатных дверей &gt; Дверные ручки &gt; Aprile</t>
+        </is>
+      </c>
+      <c r="CG79" t="inlineStr">
+        <is>
+          <t>Декоративная магнитная вставка предназначена для установки в дверную ручку APRILE GUAVA WC. Модель сочетает современный дизайн с практичностью, подчёркивающими стиль и повышающим тактильный комфорт при эксплуатации. Преимущества модели – Внешняя отделка придает изделию премиальный внешний вид. – Совместимость с ручками серии APRILE GUAVA обеспечивает простую интеграцию без доработок. – Повышенная долговечность благодаря качественным материалам и точной сборке. Совместимость и монтаж Изделие предназначено для использования с дверными ручками APRILE GUAVA серии WC и монтируется внутрь ручки в специально предусмотренное посадочное место.</t>
+        </is>
+      </c>
+      <c r="CH79" t="inlineStr">
+        <is>
+          <t>https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-th-wc-1000x1000.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-th-wc-380x380.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-wh-dk-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-th-1-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-wh-wc-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-wh-dk-wc-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-bk-dk-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-wh-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-bk-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-gym-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-bk-dk-wc-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-bk-wc-200x200.png</t>
+        </is>
+      </c>
+      <c r="CI79" t="inlineStr">
+        <is>
+          <t>output/furnitura96-ru-search-search-aprile/images/vstavka-v-ruchku-aprile-guava-th-wc-pod-okrasku-428321.jpg
+output/furnitura96-ru-search-search-aprile/images/vstavka-v-ruchku-aprile-guava-th-wc-pod-okrasku-1e348c.jpg</t>
+        </is>
+      </c>
+      <c r="CJ79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Вставка в ручку APRILE GUAVA TH под окраску</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Aprile</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>РД021338</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>РД021338</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>300</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-th-1-1000x1000.png</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Италия</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Цинк</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr"/>
+      <c r="AQ80" t="inlineStr"/>
+      <c r="AR80" t="inlineStr"/>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AU80" t="inlineStr"/>
+      <c r="AV80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr"/>
+      <c r="AX80" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr"/>
+      <c r="BA80" t="inlineStr"/>
+      <c r="BB80" t="inlineStr"/>
+      <c r="BC80" t="inlineStr"/>
+      <c r="BD80" t="inlineStr"/>
+      <c r="BE80" t="inlineStr"/>
+      <c r="BF80" t="inlineStr"/>
+      <c r="BG80" t="inlineStr"/>
+      <c r="BH80" t="inlineStr"/>
+      <c r="BI80" t="inlineStr"/>
+      <c r="BJ80" t="inlineStr"/>
+      <c r="BK80" t="inlineStr"/>
+      <c r="BL80" t="inlineStr"/>
+      <c r="BM80" t="inlineStr"/>
+      <c r="BN80" t="inlineStr"/>
+      <c r="BO80" t="inlineStr"/>
+      <c r="BP80" t="inlineStr"/>
+      <c r="BQ80" t="inlineStr"/>
+      <c r="BR80" t="inlineStr"/>
+      <c r="BS80" t="inlineStr"/>
+      <c r="BT80" t="inlineStr"/>
+      <c r="BU80" t="inlineStr"/>
+      <c r="BV80" t="inlineStr"/>
+      <c r="BW80" t="inlineStr"/>
+      <c r="BX80" t="inlineStr"/>
+      <c r="BY80" t="inlineStr"/>
+      <c r="BZ80" t="inlineStr"/>
+      <c r="CA80" t="inlineStr"/>
+      <c r="CB80" t="inlineStr"/>
+      <c r="CC80" t="inlineStr"/>
+      <c r="CD80" t="inlineStr"/>
+      <c r="CE80" t="inlineStr">
+        <is>
+          <t>https://furnitura96.ru/vstavka-v-ruchku-aprile-guava-th-pod-okrasku/</t>
+        </is>
+      </c>
+      <c r="CF80" t="inlineStr">
+        <is>
+          <t>Фурнитура для межкомнатных дверей &gt; Дверные ручки &gt; Aprile</t>
+        </is>
+      </c>
+      <c r="CG80" t="inlineStr">
+        <is>
+          <t>Декоративная магнитная вставка предназначена для установки в дверную ручку APRILE GUAVA. Модель сочетает современный дизайн с практичностью, подчёркивающими стиль и повышающим тактильный комфорт при эксплуатации. Преимущества модели – Внешняя отделка придает изделию премиальный внешний вид. – Совместимость с ручками серии APRILE GUAVA обеспечивает простую интеграцию без доработок. – Повышенная долговечность благодаря качественным материалам и точной сборке. Совместимость и монтаж Изделие предназначено для использования с дверными ручками APRILE GUAVA серии WC и монтируется внутрь ручки в специально предусмотренное посадочное место.</t>
+        </is>
+      </c>
+      <c r="CH80" t="inlineStr">
+        <is>
+          <t>https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-th-1-1000x1000.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-th-1-380x380.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-wh-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-bk-dk-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-bk-dk-wc-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-gym-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-th-wc-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-wh-dk-wc-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-bk-wc-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-bk-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-wh-wc-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile/big-vstavka-v-ruchku-wh-dk-200x200.png</t>
+        </is>
+      </c>
+      <c r="CI80" t="inlineStr">
+        <is>
+          <t>output/furnitura96-ru-search-search-aprile/images/vstavka-v-ruchku-aprile-guava-th-pod-okrasku-bb34ea.jpg
+output/furnitura96-ru-search-search-aprile/images/vstavka-v-ruchku-aprile-guava-th-pod-okrasku-fb414b.jpg</t>
+        </is>
+      </c>
+      <c r="CJ80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Ручка APRILE ROSA R 7S BK</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Aprile</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>РД021773</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Черный</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>РД021773</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>600</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile//ges-upload-1065-bk-1000x1000.png</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Италия</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Латунь</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>2 года</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>На круглой розетке</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>Черный</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr"/>
+      <c r="AQ81" t="inlineStr"/>
+      <c r="AR81" t="inlineStr"/>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AU81" t="inlineStr"/>
+      <c r="AV81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr"/>
+      <c r="AX81" t="inlineStr"/>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr"/>
+      <c r="BA81" t="inlineStr"/>
+      <c r="BB81" t="inlineStr"/>
+      <c r="BC81" t="inlineStr"/>
+      <c r="BD81" t="inlineStr"/>
+      <c r="BE81" t="inlineStr"/>
+      <c r="BF81" t="inlineStr"/>
+      <c r="BG81" t="inlineStr"/>
+      <c r="BH81" t="inlineStr"/>
+      <c r="BI81" t="inlineStr"/>
+      <c r="BJ81" t="inlineStr"/>
+      <c r="BK81" t="inlineStr"/>
+      <c r="BL81" t="inlineStr"/>
+      <c r="BM81" t="inlineStr"/>
+      <c r="BN81" t="inlineStr"/>
+      <c r="BO81" t="inlineStr"/>
+      <c r="BP81" t="inlineStr"/>
+      <c r="BQ81" t="inlineStr"/>
+      <c r="BR81" t="inlineStr"/>
+      <c r="BS81" t="inlineStr"/>
+      <c r="BT81" t="inlineStr"/>
+      <c r="BU81" t="inlineStr"/>
+      <c r="BV81" t="inlineStr"/>
+      <c r="BW81" t="inlineStr"/>
+      <c r="BX81" t="inlineStr"/>
+      <c r="BY81" t="inlineStr"/>
+      <c r="BZ81" t="inlineStr"/>
+      <c r="CA81" t="inlineStr"/>
+      <c r="CB81" t="inlineStr"/>
+      <c r="CC81" t="inlineStr"/>
+      <c r="CD81" t="inlineStr"/>
+      <c r="CE81" t="inlineStr">
+        <is>
+          <t>https://furnitura96.ru/ruchka-aprile-rosa-r-7s-bk-chernyj/</t>
+        </is>
+      </c>
+      <c r="CF81" t="inlineStr">
+        <is>
+          <t>Фурнитура для межкомнатных дверей &gt; Дверные ручки &gt; Aprile</t>
+        </is>
+      </c>
+      <c r="CG81" t="inlineStr">
+        <is>
+          <t>Ручка APRILE ROSA R 7S BK Черный - это тщательно отобранная модель ручки лучшим европейским дизайнером. Высококачественные материалы, передовые технологии и опыт авторитетных европейских производителей - гарантия наилучшего исполнения и комфортного использования каждой ручки На круглой розетке с логотипом APRILE. Разнообразие цветового решения и стиля придаст вашему интерьеру индивидуальность и изысканность. Дверные ручки Aprile в цвете Черный создаются для клиентов, которые ищут оригинальные, но уравновешенные формы, далекие от манерного дизайна и кратковременных трендов.</t>
+        </is>
+      </c>
+      <c r="CH81" t="inlineStr">
+        <is>
+          <t>https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile//ges-upload-1065-bk-1000x1000.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile//ges-upload-1065-bk-380x380.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile//ges-upload-1361-bk-200x200.jpg
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile//ges-upload-1061-bk-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile//ges-upload-1341-tulipa-r-7s-bk-2-200x200.jpg
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile//ges-upload-1359-bk-200x200.jpg
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile//ges-upload-1339-alora-r-7s-bk-2-200x200.jpg
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile//ges-upload-1046-bk-200x200.jpg
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile//ges-upload-1204-bk-200x200.jpg
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile//ges-upload-1201-bk-200x200.jpg
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile//ges-upload-1059-bk-200x200.png
+https://furnitura96.ru/image/cache/catalog/products/furnitura-dlya-mezhkomnatnih-dverej/dvernie-ruchki/aprile//ges-upload-1351-bk-200x200.jpg</t>
+        </is>
+      </c>
+      <c r="CI81" t="inlineStr">
+        <is>
+          <t>output/furnitura96-ru-search-search-aprile/images/ruchka-aprile-rosa-r-7s-bk-chernyy-dea653.jpg
+output/furnitura96-ru-search-search-aprile/images/ruchka-aprile-rosa-r-7s-bk-chernyy-92aa9f.jpg</t>
+        </is>
+      </c>
+      <c r="CJ81" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/все-товары.xlsx
+++ b/output/все-товары.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ81"/>
+  <dimension ref="A1:CJ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13647,6 +13647,146 @@
       </c>
       <c r="CJ81" t="inlineStr"/>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Дверная ручка ROBOT, произведено в Италии</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="n">
+        <v>9100</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>https://union.ru/upload/iblock/c7c/48l83u3a3ul443213lcok54t0ahnuw21/ROBOT-2400x1600.jpg</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr"/>
+      <c r="AP82" t="inlineStr"/>
+      <c r="AQ82" t="inlineStr"/>
+      <c r="AR82" t="inlineStr"/>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AU82" t="inlineStr"/>
+      <c r="AV82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr"/>
+      <c r="AX82" t="inlineStr"/>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr"/>
+      <c r="BA82" t="inlineStr"/>
+      <c r="BB82" t="inlineStr"/>
+      <c r="BC82" t="inlineStr"/>
+      <c r="BD82" t="inlineStr"/>
+      <c r="BE82" t="inlineStr"/>
+      <c r="BF82" t="inlineStr"/>
+      <c r="BG82" t="inlineStr"/>
+      <c r="BH82" t="inlineStr"/>
+      <c r="BI82" t="inlineStr"/>
+      <c r="BJ82" t="inlineStr"/>
+      <c r="BK82" t="inlineStr"/>
+      <c r="BL82" t="inlineStr"/>
+      <c r="BM82" t="inlineStr"/>
+      <c r="BN82" t="inlineStr"/>
+      <c r="BO82" t="inlineStr"/>
+      <c r="BP82" t="inlineStr"/>
+      <c r="BQ82" t="inlineStr"/>
+      <c r="BR82" t="inlineStr"/>
+      <c r="BS82" t="inlineStr"/>
+      <c r="BT82" t="inlineStr"/>
+      <c r="BU82" t="inlineStr"/>
+      <c r="BV82" t="inlineStr"/>
+      <c r="BW82" t="inlineStr"/>
+      <c r="BX82" t="inlineStr"/>
+      <c r="BY82" t="inlineStr"/>
+      <c r="BZ82" t="inlineStr"/>
+      <c r="CA82" t="inlineStr"/>
+      <c r="CB82" t="inlineStr"/>
+      <c r="CC82" t="inlineStr"/>
+      <c r="CD82" t="inlineStr"/>
+      <c r="CE82" t="inlineStr">
+        <is>
+          <t>https://union.ru/catalog-hardware/ruchki-dlya-mezhkomnatnykh-dverey/colombo-made-in-italy/robot-crom/</t>
+        </is>
+      </c>
+      <c r="CF82" t="inlineStr">
+        <is>
+          <t>Каталог фурнитура &gt; Ручки для межкомнатных дверей &gt; COLOMBO (производство в Италии) &gt; ROBOT, Хром</t>
+        </is>
+      </c>
+      <c r="CG82" t="inlineStr">
+        <is>
+          <t>Colombo Design по праву является лидером среди производителей ручек для входных и межкомнатных дверей. Это достигается совершенством технологии и сотрудничеством с известными дизайн-студиями, такими как BARTOLI, PININFARINA, CASTILIA и др. На все ручки дается заводская гарантия от 10 до 30 лет.</t>
+        </is>
+      </c>
+      <c r="CH82" t="inlineStr">
+        <is>
+          <t>https://union.ru/upload/iblock/c7c/48l83u3a3ul443213lcok54t0ahnuw21/ROBOT-2400x1600.jpg
+https://union.ru/upload/iblock/924/nj7qiueafpmce6qb21tj84fgu0g3rlqd/ROBOT_2400kh1600.png
+https://union.ru/upload/delight.webpconverter/upload/resize_cache/iblock/c7c/48l83u3a3ul443213lcok54t0ahnuw21/1000_450_1/ROBOT-2400x1600.jpg.webp?17891217398880
+https://union.ru/upload/delight.webpconverter/upload/resize_cache/iblock/924/nj7qiueafpmce6qb21tj84fgu0g3rlqd/1000_450_1/ROBOT_2400kh1600.png.webp?1789121732122762
+https://union.ru/upload/delight.webpconverter/upload/resize_cache/iblock/c7c/48l83u3a3ul443213lcok54t0ahnuw21/0_150_1/ROBOT-2400x1600.jpg.webp?178912173940842
+https://union.ru/upload/delight.webpconverter/upload/resize_cache/iblock/924/nj7qiueafpmce6qb21tj84fgu0g3rlqd/0_150_1/ROBOT_2400kh1600.png.webp?1789121733491274
+https://union.ru/upload/iblock/ad0/dg52bb5fefeonynoq563c6vf98l219oo/05-Cromo.jpg
+https://union.ru/upload/iblock/949/hijqewoxzrnfl6am7yq59isf1s8j03mu/06-Cromat.jpg
+https://union.ru/upload/iblock/810/qhxq9v1yq8sy3pie07hhoiuo9ef0jlg1/02-Oroplus.jpg
+https://union.ru/upload/delight.webpconverter/upload/iblock/b6e/0z1122bj7ss7xms4jq261jy1zpuyvj9r/1420-x-64-px_01_01.jpg.webp?179162811725410
+https://union.ru/upload/delight.webpconverter/includes/consul/cons_p.png.webp?17891193782034
+https://union.ru/upload/delight.webpconverter/includes/consul/obmer_p.png.webp?17891193781342</t>
+        </is>
+      </c>
+      <c r="CI82" t="inlineStr">
+        <is>
+          <t>output/union-ru-catalog-hardware-ruchki-dlya-mezhkomnatnykh-dverey/images/dvernaya-ruchka-robot-proizvedeno-v-italii-3540d2.jpg
+output/union-ru-catalog-hardware-ruchki-dlya-mezhkomnatnykh-dverey/images/dvernaya-ruchka-robot-proizvedeno-v-italii-ba3098.jpg
+output/union-ru-catalog-hardware-ruchki-dlya-mezhkomnatnykh-dverey/images/dvernaya-ruchka-robot-proizvedeno-v-italii-dc21a0.jpg
+output/union-ru-catalog-hardware-ruchki-dlya-mezhkomnatnykh-dverey/images/dvernaya-ruchka-robot-proizvedeno-v-italii-9bbb82.jpg
+output/union-ru-catalog-hardware-ruchki-dlya-mezhkomnatnykh-dverey/images/dvernaya-ruchka-robot-proizvedeno-v-italii-4f3c27.jpg
+output/union-ru-catalog-hardware-ruchki-dlya-mezhkomnatnykh-dverey/images/dvernaya-ruchka-robot-proizvedeno-v-italii-9ee4d2.jpg</t>
+        </is>
+      </c>
+      <c r="CJ82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
